--- a/data/HMD_Jew_doc.xlsx
+++ b/data/HMD_Jew_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edina\Dropbox\ACLSStudium\FS 2026\Deep Learning\Group project\Topic classification of historical political programs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B5D25C5-9B08-4E35-B3D5-9A4AD04187BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3314540B-95C0-4E23-80FD-342749A56506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4474CFA4-FE31-4005-B69E-0EDDA9267F66}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>doc_title</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>zion</t>
+  </si>
+  <si>
+    <t>doc_lan</t>
+  </si>
+  <si>
+    <t>ger</t>
   </si>
 </sst>
 </file>
@@ -506,126 +512,144 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA8F67A-2BD6-44C6-9F0C-E6BC22E58890}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1907</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1911</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>1911</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>1911</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>1909</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>23</v>
       </c>
     </row>
